--- a/tools/advisor_ref_output/AI访谈材料.xlsx
+++ b/tools/advisor_ref_output/AI访谈材料.xlsx
@@ -117,12 +117,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -177,7 +177,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -204,12 +204,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -264,7 +264,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -291,12 +291,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -465,12 +465,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2205,67 +2205,67 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2292,67 +2292,67 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2379,42 +2379,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2424,22 +2424,22 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -11079,67 +11079,67 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -11166,67 +11166,67 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -11427,12 +11427,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">

--- a/tools/advisor_ref_output/AI访谈材料.xlsx
+++ b/tools/advisor_ref_output/AI访谈材料.xlsx
@@ -204,47 +204,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -254,17 +254,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -465,67 +465,67 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -552,67 +552,67 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -639,42 +639,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -726,67 +726,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -987,67 +987,67 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1074,67 +1074,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1596,67 +1596,67 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1770,67 +1770,67 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1944,67 +1944,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2031,47 +2031,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2118,67 +2118,67 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2205,42 +2205,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2292,67 +2292,67 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2379,67 +2379,67 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2466,42 +2466,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2511,22 +2511,22 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2553,47 +2553,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2640,42 +2640,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2685,22 +2685,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2727,67 +2727,67 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2814,47 +2814,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2901,67 +2901,67 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3075,67 +3075,67 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3162,67 +3162,67 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t/>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t/>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3249,42 +3249,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3294,22 +3294,22 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3336,42 +3336,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3381,22 +3381,22 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3510,42 +3510,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3560,17 +3560,17 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3597,47 +3597,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3684,67 +3684,67 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3771,67 +3771,67 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3858,67 +3858,67 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3945,42 +3945,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3995,17 +3995,17 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4032,42 +4032,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4077,22 +4077,22 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4119,47 +4119,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4169,17 +4169,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4206,42 +4206,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4251,22 +4251,22 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4380,67 +4380,67 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t/>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t/>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t/>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4467,67 +4467,67 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4641,42 +4641,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4815,67 +4815,67 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4902,67 +4902,67 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5076,42 +5076,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5250,67 +5250,67 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5337,67 +5337,67 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5424,42 +5424,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5469,22 +5469,22 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5946,47 +5946,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6033,67 +6033,67 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6381,42 +6381,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6468,67 +6468,67 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6555,67 +6555,67 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6642,67 +6642,67 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t/>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t/>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6729,67 +6729,67 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6816,67 +6816,67 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6903,67 +6903,67 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6990,67 +6990,67 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7077,67 +7077,67 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7164,67 +7164,67 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7251,67 +7251,67 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7425,42 +7425,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7512,47 +7512,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7562,17 +7562,17 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7599,47 +7599,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7649,17 +7649,17 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7686,42 +7686,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7731,22 +7731,22 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7773,67 +7773,67 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8034,67 +8034,67 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8208,47 +8208,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8258,17 +8258,17 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8295,42 +8295,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8340,22 +8340,22 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8382,42 +8382,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -8469,67 +8469,67 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t/>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t/>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t/>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t/>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8556,67 +8556,67 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8643,67 +8643,67 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8817,42 +8817,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8862,22 +8862,22 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -8904,42 +8904,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8991,67 +8991,67 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9078,67 +9078,67 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t/>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t/>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t/>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -9165,47 +9165,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9215,17 +9215,17 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -9252,67 +9252,67 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -9339,67 +9339,67 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -9600,42 +9600,42 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9645,22 +9645,22 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9774,42 +9774,42 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9819,22 +9819,22 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -9861,67 +9861,67 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -10035,67 +10035,67 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -10209,67 +10209,67 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t/>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -10296,42 +10296,42 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10341,22 +10341,22 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -10383,67 +10383,67 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -10470,67 +10470,67 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t/>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t/>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t/>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -10818,67 +10818,67 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -11079,42 +11079,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11124,22 +11124,22 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -11166,67 +11166,67 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -11427,67 +11427,67 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -11601,42 +11601,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11651,17 +11651,17 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -11688,47 +11688,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -11738,17 +11738,17 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -11775,42 +11775,42 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11825,17 +11825,17 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">

--- a/tools/advisor_ref_output/AI访谈材料.xlsx
+++ b/tools/advisor_ref_output/AI访谈材料.xlsx
@@ -204,47 +204,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -254,17 +254,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t/>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -465,67 +465,67 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -552,67 +552,67 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -639,42 +639,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -726,67 +726,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -900,67 +900,67 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -987,42 +987,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1074,67 +1074,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1248,67 +1248,67 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1509,67 +1509,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1596,67 +1596,67 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1683,42 +1683,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1728,22 +1728,22 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1770,67 +1770,67 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1857,67 +1857,67 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2031,42 +2031,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2076,22 +2076,22 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2205,42 +2205,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2292,67 +2292,67 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2379,67 +2379,67 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2466,42 +2466,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2511,22 +2511,22 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2553,47 +2553,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2640,42 +2640,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2685,22 +2685,22 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/D</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2727,47 +2727,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2814,47 +2814,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3075,42 +3075,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3120,22 +3120,22 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3336,67 +3336,67 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3510,67 +3510,67 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3597,47 +3597,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3684,42 +3684,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3858,67 +3858,67 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3945,67 +3945,67 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">未参与小组建构</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4032,42 +4032,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4077,22 +4077,22 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4119,67 +4119,67 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4293,67 +4293,67 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4380,42 +4380,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4467,67 +4467,67 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4815,67 +4815,67 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t/>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t/>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4902,67 +4902,67 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t/>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t/>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4989,47 +4989,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t/>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5337,67 +5337,67 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5424,42 +5424,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5469,22 +5469,22 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5598,67 +5598,67 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5946,67 +5946,67 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6294,67 +6294,67 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t/>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6381,67 +6381,67 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">未参与小组建构</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中。；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第4题这个情境。当时的情境是：大班建构活动中，睿睿和其他幼儿计划一起搭积木大桥，他们讨论了搭建方法，并进入区域开始搭建。就在其他幼儿在认真搭建时，睿睿发现了一块长条木板，他一会儿在地上推着走，一会儿当枪使，没有再参与小组的搭建。当时提供的做法包括：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中；教师C：引导睿睿回顾计划，建议他先完成共同任务，长条木板可以等自由游戏时再玩；教师D：看到睿睿玩得开心，暂不介入，等下一次活动时再提醒他根据计划开展游戏。可以先从这个情境本身追问：睿睿离开了原来的搭桥计划去玩长条木板，你当时怎样理解他的行为：是偏离共同任务，还是出现了新的游戏线索？；面对共同建构计划和幼儿临时兴趣之间的变化，你觉得教师什么时候应该介入，什么时候可以继续观察？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：继续观察，后续分享中支持睿睿思考如何把长条木板融入小组的建构中；教师B：肯定睿睿的创造性玩法，询问他长条板能否当桥面，引导他参与到搭桥任务中？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6468,42 +6468,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6513,22 +6513,22 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6555,67 +6555,67 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6729,42 +6729,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6774,22 +6774,22 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6990,47 +6990,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7040,17 +7040,17 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7164,42 +7164,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7209,22 +7209,22 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7425,42 +7425,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7475,17 +7475,17 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7773,67 +7773,67 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8034,67 +8034,67 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8208,47 +8208,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">消防员救火开心</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8258,17 +8258,17 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
+          <t xml:space="preserve">教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8295,42 +8295,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8340,22 +8340,22 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8382,42 +8382,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -8469,67 +8469,67 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8556,67 +8556,67 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t/>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t/>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8643,67 +8643,67 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8730,67 +8730,67 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8904,67 +8904,67 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域停留短</t>
+          <t xml:space="preserve">艾莎公主不运动</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
+          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
+          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
+          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
+          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8991,67 +8991,67 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/B</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9078,67 +9078,67 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -9165,47 +9165,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9215,17 +9215,17 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -9252,67 +9252,67 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">篮球架玩水</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/D</t>
+          <t xml:space="preserve">A/B</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -9339,67 +9339,67 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">A/C</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -9774,42 +9774,42 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">艾莎公主不运动</t>
+          <t xml:space="preserve">跳绳秩序混乱</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。</t>
+          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动。</t>
+          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。</t>
+          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动。</t>
+          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏。；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。</t>
+          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第7题这个情境。当时的情境是：小班的一次户外运动，有几个女孩子从一开始就没有选择任何体育活动项目，而是聚在一起坐在地上玩“艾莎公主”的游戏，比一比谁的鞋子最漂亮，谁的魔法最厉害。当时提供的做法包括：教师A：询问幼儿没有参与运动的原因，提供丰富的活动材料吸引幼儿参与运动活动；教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师C：利用艾莎公主的鞋子设计走、跑、跳等活动，并以参与者的身份邀请幼儿一起参与运动；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动。可以先从这个情境本身追问：几个女孩在户外运动时间玩艾莎公主时，你当时更关注运动目标，还是关注她们正在生成的角色游戏兴趣？；如果要把艾莎公主游戏和运动活动连接起来，你觉得教师可以怎样做才不显得生硬？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：提醒幼儿现在是运动时间，请他们等自由游戏时间再一起玩“艾莎公主”的游戏；教师D：肯定幼儿自主游戏的行为，言语引导幼儿穿着“漂亮的鞋子”参与运动？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -9948,42 +9948,42 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q10</t>
+          <t xml:space="preserve">Q9</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">跳绳秩序混乱</t>
+          <t xml:space="preserve">飞行棋各走各的</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。</t>
+          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏。</t>
+          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。</t>
+          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9993,22 +9993,22 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏。</t>
+          <t xml:space="preserve">教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则。；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。</t>
+          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第10题这个情境。当时的情境是：周三下午，大五班的幼儿正自发进行跳绳游戏。李老师观察后发现，挤在一起跳绳的幼儿人数较多，整个场面十分混乱，幼儿很容易出现碰撞现象。此外，由于当“柱子”的幼儿很久才能轮上跳绳，因此也显得很不耐烦。当时提供的做法包括：教师A：请幼儿暂停游戏，将幼儿分成多个小组并引导他们以小组为单位分区域开展游戏；教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师C：提供更多数量和不同种类的跳绳，并言语引导幼儿分组分区同时进行跳绳游戏；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法。可以先从这个情境本身追问：跳绳现场混乱且可能碰撞时，你当时更倾向于立即组织秩序，还是先让幼儿自己发现问题？；在安全风险和幼儿自主制定规则之间，你觉得教师应该怎样把握介入时机？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：请幼儿说一说跳绳活动中存在的问题，并邀请幼儿一起设置跳绳的规则；教师D：暂不介入，活动分享时通过照片或视频回放引导幼儿发现问题并商议解决办法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -10296,67 +10296,67 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t/>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">C/D</t>
+          <t/>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t/>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t/>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -10383,42 +10383,42 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">A/C</t>
+          <t xml:space="preserve">C/D</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -10470,67 +10470,67 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可追问：你当时主要依据什么来排列这些做法？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -11079,42 +11079,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q9</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行棋各走各的</t>
+          <t xml:space="preserve">频繁求助</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。</t>
+          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导。</t>
+          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。</t>
+          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11124,22 +11124,22 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/C</t>
+          <t xml:space="preserve">B/D</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题。；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏。</t>
+          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第9题这个情境。当时的情境是：大班区域游戏中，轩轩和小宇一起玩飞行棋，他们将棋子摆好后，各自拿了一个骰子开始投，小宇说：“该我走。”轩轩说：“明明该我走！”相持不下，于是两人各拿一个骰子，自顾自地走自己的棋。当时提供的做法包括：教师A：耐心讲解共同游戏的规则，再以“棋手”身份加入游戏进行示范引导；教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏；教师D：待幼儿体验一轮各走各的游戏后，询问幼儿的游戏体验，提示共同游戏规则的作用。可以先从这个情境本身追问：两个孩子各走各的棋时，你当时更关注共同游戏规则的建立，还是先让他们体验这种玩法会带来什么问题？；你觉得教师怎样帮助幼儿从各玩各的，过渡到真正的共同游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，继续观察游戏进展，待区域小结时请幼儿分享游戏中的体验和问题；教师C：拿走一个骰子，请幼儿商量只有一个骰子的共同游戏规则，达成一致后再开始游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -11166,67 +11166,67 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">频繁求助</t>
+          <t xml:space="preserve">材料选择无层次</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。</t>
+          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力。</t>
+          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤。</t>
+          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">B/D</t>
+          <t xml:space="preserve">B/C</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。</t>
+          <t xml:space="preserve">教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建。；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。</t>
+          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第2题这个情境。当时的情境是：中班区域活动时，小明选择了建构区。玩了一会儿，他跑到老师面前说“老师，我不会搭……帮帮我吧”，教师问他需要什么帮助时，他一边说我不会搭，一边却很快地将房子从一层积木加高到了两层。看小明专注搭建后，老师就离开建构区了。可是没一会，小明又找了老师好几次，说“老师，帮帮我吧，我不会搭”。当时提供的做法包括：教师A：鼓励小明独立搭建，引导他思考接下来如何搭建，及时表扬他的努力；教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师C：在旁观察小明的搭建过程，并适时反馈，帮助他理清搭建步骤；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现。可以先从这个情境本身追问：小明一边说不会搭，一边又能继续加高房子，你当时怎样判断他真正需要的帮助是什么？；面对幼儿反复求助，你觉得教师怎样支持，既不替代幼儿完成，又能帮助他继续推进游戏？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：先示范搭建关键部分，请小明观察方法，再鼓励他照着继续搭建；教师D：帮小明回顾已搭建完成的部分，指导他设定小目标，尝试自己实现？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -11601,42 +11601,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">Q8</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">材料选择无层次</t>
+          <t xml:space="preserve">引水难题未解</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。</t>
+          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡。</t>
+          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。</t>
+          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11651,17 +11651,17 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。</t>
+          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累。；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战。</t>
+          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第6题这个情境。当时的情境是：大班上学期，张老师在建构区投放了按图搭建的游戏材料，并提供了不同星级难度的任务卡供幼儿选择，但有的幼儿一上来就选择高难度的三星级任务卡，结果不能顺利完成任务；而有的幼儿始终选择低难度的一星级任务卡。这天，浩浩又连续选择了几张一星级任务卡，很快就完成了任务。当时提供的做法包括：教师A：调整任务卡提供方式，在游戏开始前根据幼儿的能力水平有针对性地发放任务卡；教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战；教师D：和浩浩回顾已完成的任务，比较不同星级的难度，邀请他选择稍有挑战的任务。可以先从这个情境本身追问：浩浩反复选择一星任务卡时，你当时更想尊重他的自主选择，还是推动他尝试更有挑战的任务？；你觉得教师应该怎样判断幼儿是需要安全感、缺少挑战意识，还是任务卡呈现方式本身需要调整？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：暂不介入，尊重幼儿的自主选择和游戏体验，只要完成任务就是一种经验积累；教师C：调整任务卡呈现方式，如增加“我想挑战”等提示，鼓励幼儿选择不同星级的挑战？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -11688,47 +11688,47 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">篮球架玩水</t>
+          <t xml:space="preserve">消防员救火开心</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。</t>
+          <t xml:space="preserve">近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性。</t>
+          <t xml:space="preserve">抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡。</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。</t>
+          <t xml:space="preserve">请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -11738,17 +11738,17 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。</t>
+          <t xml:space="preserve">教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水。；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏。</t>
+          <t xml:space="preserve">教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救？；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的。</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第1题这个情境。当时的情境是：操场上新安装了一些篮球架，幼儿经常在这里投篮。某天户外活动时，几名幼儿带着画笔和水桶来到这里，他们先是快乐地粉刷篮球架，之后开始往篮框里灌水，有的从上面灌，有的在下面接，忙的不亦乐乎，俨然这里成为了玩水的场地。当时提供的做法包括：教师A：看到幼儿玩得很开心，不干预他们的玩水行为，待兴趣减弱后再讨论玩水的适宜性；教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏；教师D：提醒幼儿篮球架是用于开展运动的，与其他幼儿一起召唤他们打篮球，转移他们的关注点。可以先从这个情境本身追问：这个情境里，孩子把篮球架变成玩水场地，你当时更关注他们的游戏兴趣、器械用途，还是安全与场地适宜性？；如果既想保护孩子的探索兴趣，又要回应篮球架原本的运动功能，你觉得教师可以怎样衔接？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：表扬幼儿的新发现，并询问在篮球架旁玩水是否合适，提议幼儿可以换个地方玩水；教师C：参与到幼儿的“粉刷”游戏中，逐步引导幼儿到适宜玩水的地方继续开展游戏？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第5题这个情境。当时的情境是：近几天，中班的幼儿十分热衷于在区域游戏时间玩“消防员救火”的游戏。游戏结束后的交流活动中，老师问幼儿最想分享什么时，阳阳说“娃娃家着火了，好开心啊！”。当时提供的做法包括：教师A：抓住教育契机，向幼儿耐心解释真实的火灾会造成物品损失和人员伤亡；教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的；教师D：请阳阳讲讲娃娃家着火后发生了什么、为什么开心，借此理解幼儿的游戏体验。可以先从这个情境本身追问：阳阳说娃娃家着火了很开心时，你当时更关注真实火灾的危险教育，还是先理解他在游戏里的开心来自哪里？；你觉得教师怎样回应，既不否定幼儿的游戏体验，又能引导他们理解真实火灾的意义？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：询问幼儿开心的是“着火”本身，还是消防员成功救火、娃娃家的人得救；教师C：引导幼儿思考“娃娃家着火”值不值得开心，帮助他们认识真实火灾是危险的？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -11775,47 +11775,47 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q8</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">引水难题未解</t>
+          <t xml:space="preserve">区域停留短</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。</t>
+          <t xml:space="preserve">小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试。</t>
+          <t xml:space="preserve">提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。</t>
+          <t xml:space="preserve">游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -11825,17 +11825,17 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。</t>
+          <t xml:space="preserve">教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享。</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式。；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试。</t>
+          <t xml:space="preserve">教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友。；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因。</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">请回忆第8题这个情境。当时的情境是：中班上学期，幼儿在“引水游戏”中遇到了难题——水无法被引到竹片管道上。他们不断调整竹片拼接的方式，却始终没能成功，即竹片一头高于出水管道，阻碍了引流。渐渐地幼儿的探索兴趣也减弱了，有的开始玩水，有的甚至离开了水池。当时提供的做法包括：教师A：示范正确的引水方法，请幼儿注意观察并说说引水的要领，再自己试一试；教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试；教师D：投放更多辅助引水的材料，重新激起幼儿的探索兴趣，继续观察游戏进展。可以先从这个情境本身追问：孩子们引水失败、兴趣减弱时，你当时更倾向于直接示范方法，还是继续支持他们自己发现水流受阻的原因？；你觉得教师怎样提供支架，既能帮助问题解决，又保留幼儿继续探究的空间？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：加入幼儿的探索，引导他们观察水流受阻的位置，一起尝试调整竹片的摆放方式；教师C：组织幼儿就游戏困难进行讨论，寻找解决问题的方案，引导幼儿再次尝试？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
+          <t xml:space="preserve">请回忆第3题这个情境。当时的情境是：小班幼儿瑶瑶在区域活动时，一会儿在娃娃家切切菜，一会儿到美工区搓搓橡皮泥，一会儿又开心地跑到其它区域游戏，在任何一个区域停留时间都不超过三分钟。当时提供的做法包括：教师A：提议瑶瑶完成某项游戏任务，如在娃娃家做菜，请他活动小结时分享；教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因；教师D：以同伴的身份陪伴瑶瑶在某一区域游戏，待他专注游戏后再离开。可以先从这个情境本身追问：瑶瑶在多个区域快速转换时，你当时会先把它看作注意力不集中、规则问题，还是一种探索不同材料的方式？；如果你在现场，你会先观察哪些信息来判断是否需要介入？。然后可围绕其作答过程中的重点比较追问：你当时是怎样比较以下两种做法的：教师B：游戏前提醒区域活动规则，活动结束后表扬区域游戏规则遵守得好的小朋友；教师C：仔细观察瑶瑶在不同区域的游戏情况，分析他发生迅速转移的原因？如果教师提到调整过顺序，再追问：是什么信息或想法让你改变了当时的排序？请只围绕情境理解、判断依据和选项比较提问，不要提及任何内部计算指标、得分、排名、入选原因或评价性判断。</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
